--- a/Stocks/IBS.xlsx
+++ b/Stocks/IBS.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://academiafaedupt-my.sharepoint.com/personal/sbclemente_academiafa_edu_pt/Documents/Gigs/WorkingFolder/Finance_Shared/Stocks/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3D08330E-0DD8-496C-B542-851CDA9E01C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="8_{3D08330E-0DD8-496C-B542-851CDA9E01C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6F291547-5648-49A4-8C59-373EEBC2484D}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{011223E6-2324-46A7-A836-8C26C45CF533}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{011223E6-2324-46A7-A836-8C26C45CF533}"/>
   </bookViews>
   <sheets>
-    <sheet name="Folha1" sheetId="1" r:id="rId1"/>
+    <sheet name="main" sheetId="1" r:id="rId1"/>
+    <sheet name="model" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -484,4 +485,13 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{642F5327-6167-4DAE-BBAC-80D231867439}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>